--- a/lojas-proprias/pwr_reports_mensal/Keys Summary - Lojas Corporativas (Stores)(2026-09-01 - 2026-09-06).xlsx
+++ b/lojas-proprias/pwr_reports_mensal/Keys Summary - Lojas Corporativas (Stores)(2026-09-01 - 2026-09-06).xlsx
@@ -207,30 +207,30 @@
 20</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>R$ 1.101.959,95</t>
-  </si>
-  <si>
-    <t>R$ 52.474,28
-R$ 52.598,39</t>
-  </si>
-  <si>
-    <t>4.0%
-4.3%</t>
-  </si>
-  <si>
-    <t>572.8</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>30.2%</t>
-  </si>
-  <si>
-    <t>(7.0%)</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>R$ 1.116.721,45</t>
+  </si>
+  <si>
+    <t>R$ 53.177,21
+R$ 53.336,46</t>
+  </si>
+  <si>
+    <t>4.2%
+4.5%</t>
+  </si>
+  <si>
+    <t>580.0</t>
+  </si>
+  <si>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>30.5%</t>
+  </si>
+  <si>
+    <t>(6.6%)</t>
   </si>
   <si>
     <t>3.2%</t>
@@ -239,10 +239,10 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>25.0</t>
-  </si>
-  <si>
-    <t>76.8%</t>
+    <t>25.1</t>
+  </si>
+  <si>
+    <t>76.2%</t>
   </si>
   <si>
     <t>5.8%</t>
@@ -254,13 +254,13 @@
     <t>4.0</t>
   </si>
   <si>
-    <t>10.7</t>
+    <t>11.4</t>
   </si>
   <si>
     <t>18.0</t>
   </si>
   <si>
-    <t>80.7%</t>
+    <t>80.3%</t>
   </si>
   <si>
     <t>-R$ 10.109,93</t>
@@ -951,7 +951,7 @@
         <v>5.0960209459459458</v>
       </c>
       <c r="AC2" s="8">
-        <v>9.6781780000000008</v>
+        <v>11.786137</v>
       </c>
       <c r="AD2" s="8">
         <v>18.63966688888889</v>
@@ -1082,7 +1082,7 @@
         <v>4.277457793764988</v>
       </c>
       <c r="AC3" s="8">
-        <v>11.736893999999999</v>
+        <v>12.36811</v>
       </c>
       <c r="AD3" s="8">
         <v>17.594736842105263</v>
@@ -1213,7 +1213,7 @@
         <v>2.479621380846325</v>
       </c>
       <c r="AC4" s="8">
-        <v>10.872907</v>
+        <v>10.466931000000001</v>
       </c>
       <c r="AD4" s="8">
         <v>17.306295414847163</v>
@@ -1344,7 +1344,7 @@
         <v>3.8974808139534884</v>
       </c>
       <c r="AC5" s="8">
-        <v>9.1806400000000004</v>
+        <v>9.7179079999999995</v>
       </c>
       <c r="AD5" s="8">
         <v>16.618792173913043</v>
@@ -1477,7 +1477,7 @@
         <v>4.2591384269662926</v>
       </c>
       <c r="AC6" s="8">
-        <v>17.098393000000002</v>
+        <v>16.066929999999999</v>
       </c>
       <c r="AD6" s="8">
         <v>23.00681640449438</v>
@@ -1608,7 +1608,7 @@
         <v>4.4369546728971958</v>
       </c>
       <c r="AC7" s="8">
-        <v>10.367595</v>
+        <v>10.593818000000001</v>
       </c>
       <c r="AD7" s="8">
         <v>16.576789838337181</v>
@@ -1737,7 +1737,7 @@
         <v>3.0437499999999997</v>
       </c>
       <c r="AC8" s="8">
-        <v>9.6944649999999992</v>
+        <v>9.5528320000000004</v>
       </c>
       <c r="AD8" s="8">
         <v>16.46536231884058</v>
@@ -1997,7 +1997,7 @@
         <v>4.6390000000000002</v>
       </c>
       <c r="AC10" s="8">
-        <v>11.377542999999999</v>
+        <v>12.5777</v>
       </c>
       <c r="AD10" s="8">
         <v>19.42326223316913</v>
@@ -2128,7 +2128,7 @@
         <v>4.0754094857142853</v>
       </c>
       <c r="AC11" s="8">
-        <v>10.045995</v>
+        <v>14.849387999999999</v>
       </c>
       <c r="AD11" s="8">
         <v>21.625930022321427</v>
@@ -2259,7 +2259,7 @@
         <v>4.4343789667896676</v>
       </c>
       <c r="AC12" s="8">
-        <v>9.4699639999999992</v>
+        <v>9.7196029999999993</v>
       </c>
       <c r="AD12" s="8">
         <v>15.597802197802197</v>
@@ -2390,7 +2390,7 @@
         <v>1.4542201923076923</v>
       </c>
       <c r="AC13" s="8">
-        <v>12.691539000000001</v>
+        <v>12.516510999999999</v>
       </c>
       <c r="AD13" s="8">
         <v>17.957893437945792</v>
@@ -2523,7 +2523,7 @@
         <v>7.4293253164556958</v>
       </c>
       <c r="AC14" s="8">
-        <v>12.428140000000001</v>
+        <v>12.791674</v>
       </c>
       <c r="AD14" s="8">
         <v>19.281720564516128</v>
@@ -2751,7 +2751,7 @@
         <v>5.6455156950672647</v>
       </c>
       <c r="AC16" s="8">
-        <v>12.793075999999999</v>
+        <v>12.241645</v>
       </c>
       <c r="AD16" s="8">
         <v>18.552380952380954</v>
@@ -2882,7 +2882,7 @@
         <v>4.0191159744408953</v>
       </c>
       <c r="AC17" s="8">
-        <v>13.180477</v>
+        <v>14.124848</v>
       </c>
       <c r="AD17" s="8">
         <v>20.881012974683543</v>
@@ -3011,7 +3011,7 @@
         <v>2.2949207619047618</v>
       </c>
       <c r="AC18" s="8">
-        <v>4.0380979999999997</v>
+        <v>4.1020989999999999</v>
       </c>
       <c r="AD18" s="8">
         <v>11.029949525616699</v>
@@ -3063,7 +3063,7 @@
         <v>19714</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C19" s="4">
         <v>44</v>
@@ -3100,55 +3100,55 @@
         <v>52</v>
       </c>
       <c r="O19" s="5">
-        <v>43590.399999999994</v>
+        <v>58351.899999999994</v>
       </c>
       <c r="P19" s="5">
-        <v>43590.399999999994</v>
+        <v>58351.899999999994</v>
       </c>
       <c r="Q19" s="6">
-        <v>0.092214478987905357</v>
+        <v>0.13074953366578401</v>
       </c>
       <c r="R19" s="7">
-        <v>444</v>
+        <v>594</v>
       </c>
       <c r="S19" s="6">
-        <v>0.1100000000000001</v>
+        <v>0.11028037383177569</v>
       </c>
       <c r="T19" s="6">
-        <v>0.29660934058875343</v>
+        <v>0.36102786198906978</v>
       </c>
       <c r="U19" s="6">
-        <v>0.0015953008001761855</v>
+        <v>0.066771291080496092</v>
       </c>
       <c r="V19" s="6">
-        <v>0.021198429011892526</v>
+        <v>0.019442503157566422</v>
       </c>
       <c r="W19" s="6">
-        <v>-0.0066193932609014822</v>
+        <v>-0.0065581926209772089</v>
       </c>
       <c r="X19" s="8">
-        <v>24.496979062499999</v>
+        <v>25.71254632516704</v>
       </c>
       <c r="Y19" s="6">
-        <v>0.74534161490683226</v>
+        <v>0.64079822616407978</v>
       </c>
       <c r="Z19" s="6">
-        <v>0.065625000000000003</v>
+        <v>0.07126948775055679</v>
       </c>
       <c r="AA19" s="8">
-        <v>6.84249592760181</v>
+        <v>7.0879907407407403</v>
       </c>
       <c r="AB19" s="8">
-        <v>3.6658779179810725</v>
+        <v>4.4033180995475112</v>
       </c>
       <c r="AC19" s="8">
         <v>10.743242</v>
       </c>
       <c r="AD19" s="8">
-        <v>17.638437187499999</v>
+        <v>18.563288641425391</v>
       </c>
       <c r="AE19" s="6">
-        <v>0.80000000000000004</v>
+        <v>0.73496659242761697</v>
       </c>
       <c r="AF19" s="9"/>
       <c r="AG19" s="5">
@@ -3246,10 +3246,10 @@
         <v>-0.04656319290465627</v>
       </c>
       <c r="T20" s="6">
-        <v>0.35345129524278285</v>
+        <v>0.34891188289374181</v>
       </c>
       <c r="U20" s="6">
-        <v>0.020559858760664951</v>
+        <v>0.016020446411623923</v>
       </c>
       <c r="V20" s="6">
         <v>0.03786520110198776</v>
@@ -3273,7 +3273,7 @@
         <v>4.2633990196078431</v>
       </c>
       <c r="AC20" s="8">
-        <v>6.8157940000000004</v>
+        <v>6.990685</v>
       </c>
       <c r="AD20" s="8">
         <v>13.938888725490196</v>
@@ -3377,10 +3377,10 @@
         <v>0.094545454545454488</v>
       </c>
       <c r="T21" s="6">
-        <v>0.3787372517112102</v>
+        <v>0.36063908471958306</v>
       </c>
       <c r="U21" s="6">
-        <v>0.05462105313640566</v>
+        <v>0.036522886144778555</v>
       </c>
       <c r="V21" s="6">
         <v>0.11469513667356276</v>
@@ -3404,7 +3404,7 @@
         <v>1.9162016759776535</v>
       </c>
       <c r="AC21" s="8">
-        <v>5.8200640000000003</v>
+        <v>5.8231900000000003</v>
       </c>
       <c r="AD21" s="8">
         <v>13.532168817204301</v>
@@ -3508,10 +3508,10 @@
         <v>0.090109890109890012</v>
       </c>
       <c r="T22" s="6">
-        <v>0.31702000533283514</v>
+        <v>0.31680217122001308</v>
       </c>
       <c r="U22" s="6">
-        <v>-0.0091176678267816738</v>
+        <v>-0.0093355019396037416</v>
       </c>
       <c r="V22" s="6">
         <v>0.019956275152688913</v>
@@ -3535,7 +3535,7 @@
         <v>4.6160493827160494</v>
       </c>
       <c r="AC22" s="8">
-        <v>9.5386830000000007</v>
+        <v>9.7773789999999998</v>
       </c>
       <c r="AD22" s="8">
         <v>15.830911330049261</v>
@@ -3666,7 +3666,7 @@
         <v>4.2087044554455444</v>
       </c>
       <c r="AC23" s="8">
-        <v>12.382507</v>
+        <v>12.685452</v>
       </c>
       <c r="AD23" s="8">
         <v>19.458639119804403</v>
